--- a/splists_raw/Zotz/83_Zotz_Epiphytes_TableS1.xlsx
+++ b/splists_raw/Zotz/83_Zotz_Epiphytes_TableS1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brissettel/Smithsonian Dropbox/Logan Brissette/A_Final_SupplementaryMaterial/83 Zotz Epiphytes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mullerh\Dropbox (Personal)\ForestGEO\SPLISTS\GitPanama_plant_species_lists\splists_raw\Zotz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62323170-DBAB-4B47-AD78-D2754B22F2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B630F4D-73F9-4AD9-8EB7-B8074D62D35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="500" windowWidth="27720" windowHeight="14600" activeTab="1" xr2:uid="{AF91DC5C-BA8F-4E1F-9681-71F7692ECBD6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF91DC5C-BA8F-4E1F-9681-71F7692ECBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="TableS1" sheetId="1" r:id="rId1"/>
@@ -1889,18 +1889,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G245"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1923,85 +1923,85 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>8</v>
@@ -2013,9 +2013,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>8</v>
@@ -2027,9 +2027,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
@@ -2041,9 +2041,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>14</v>
@@ -2055,15 +2055,15 @@
         <v>9</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>8</v>
@@ -2071,16 +2071,13 @@
       <c r="E11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
@@ -2088,16 +2085,13 @@
       <c r="E12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F12" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>8</v>
@@ -2105,13 +2099,13 @@
       <c r="E13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>8</v>
@@ -2123,26 +2117,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>8</v>
@@ -2150,101 +2147,95 @@
       <c r="E16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G17" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>38</v>
@@ -2259,12 +2250,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>38</v>
@@ -2279,66 +2267,78 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="4" t="s">
+      <c r="E27" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>55</v>
       </c>
@@ -2352,231 +2352,246 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C43" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="E43" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F43" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>9</v>
@@ -2585,15 +2600,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>77</v>
+        <v>140</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>9</v>
@@ -2602,46 +2617,43 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>9</v>
@@ -2650,35 +2662,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G49" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F49" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>9</v>
@@ -2687,15 +2690,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>9</v>
@@ -2703,36 +2703,27 @@
       <c r="F51" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G52" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F52" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>9</v>
@@ -2741,26 +2732,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>9</v>
@@ -2769,12 +2763,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>9</v>
@@ -2783,12 +2780,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>9</v>
@@ -2797,12 +2797,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>9</v>
@@ -2811,12 +2814,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>9</v>
@@ -2825,12 +2831,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>100</v>
@@ -2842,15 +2848,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>9</v>
@@ -2859,15 +2862,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>9</v>
@@ -2876,32 +2876,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>106</v>
+        <v>80</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G63" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>100</v>
+        <v>81</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>9</v>
@@ -2910,29 +2910,35 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>110</v>
+        <v>84</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G65" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>111</v>
+        <v>85</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>100</v>
+        <v>81</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>9</v>
@@ -2941,444 +2947,459 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E67" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A70" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A94" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A95" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="E95" s="4" t="s">
         <v>9</v>
       </c>
@@ -3386,12 +3407,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>126</v>
@@ -3403,9 +3421,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>126</v>
@@ -3417,9 +3435,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>126</v>
@@ -3431,9 +3449,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>159</v>
+        <v>180</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>126</v>
@@ -3445,9 +3466,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>126</v>
@@ -3459,9 +3480,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>126</v>
@@ -3473,26 +3494,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G102" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F102" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>126</v>
@@ -3504,9 +3522,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>126</v>
@@ -3518,9 +3536,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>14</v>
@@ -3531,19 +3549,13 @@
       <c r="E105" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F105" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="G105" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A106" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>169</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>126</v>
@@ -3555,12 +3567,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>171</v>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>126</v>
@@ -3568,13 +3580,16 @@
       <c r="E107" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F107" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G107" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>172</v>
+        <v>190</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>126</v>
@@ -3586,12 +3601,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109" s="5" t="s">
-        <v>173</v>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>126</v>
@@ -3603,15 +3618,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A110" s="5" t="s">
-        <v>175</v>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>176</v>
+        <v>269</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>9</v>
@@ -3620,12 +3635,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>177</v>
+        <v>270</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>9</v>
@@ -3634,12 +3652,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>178</v>
+        <v>272</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>9</v>
@@ -3648,9 +3669,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>126</v>
@@ -3662,12 +3683,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>181</v>
+        <v>195</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>126</v>
@@ -3679,12 +3700,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>182</v>
+        <v>121</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>9</v>
@@ -3693,12 +3717,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>9</v>
@@ -3707,12 +3734,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>184</v>
+        <v>274</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>9</v>
@@ -3721,237 +3751,225 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>185</v>
+        <v>276</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F118" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B119" s="4" t="s">
+      <c r="G118" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B132" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C119" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A127" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A128" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E128" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A129" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A130" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A132" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="C132" s="4" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F132" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G132" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>9</v>
@@ -3960,32 +3978,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A134" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>14</v>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G134" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A135" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>208</v>
+      <c r="F134" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>248</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>9</v>
@@ -3994,15 +4006,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A136" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>210</v>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>9</v>
@@ -4011,15 +4020,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A137" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>212</v>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>9</v>
@@ -4028,15 +4034,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A138" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>214</v>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>251</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>9</v>
@@ -4045,884 +4048,881 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G139" s="4" t="s">
+      <c r="G139" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G157" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A140" s="5" t="s">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B158" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C140" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A141" s="3" t="s">
+      <c r="C158" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C141" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A142" s="3" t="s">
+      <c r="C159" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C142" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E142" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A143" s="3" t="s">
+      <c r="C160" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C143" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A144" s="3" t="s">
+      <c r="C161" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C144" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" s="5" t="s">
+      <c r="C165" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E165" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B166" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C145" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A146" s="3" t="s">
+      <c r="C166" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E166" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B167" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C146" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" s="3" t="s">
+      <c r="C167" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C147" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A148" s="3" t="s">
+      <c r="C168" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C148" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F148" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A149" s="5" t="s">
+      <c r="C169" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B170" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C149" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" s="3" t="s">
+      <c r="C170" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B171" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C150" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A151" s="3" t="s">
+      <c r="C171" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C151" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F151" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A152" s="3" t="s">
+      <c r="C172" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C152" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E152" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A153" s="3" t="s">
+      <c r="C181" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G182" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C153" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E153" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F153" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A154" s="3" t="s">
+      <c r="C184" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C154" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E154" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F154" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A155" s="3" t="s">
+      <c r="C185" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C155" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E155" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F155" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" s="5" t="s">
+      <c r="C186" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B193" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C156" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E156" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F156" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A157" s="3" t="s">
+      <c r="C193" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C157" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E157" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F157" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A158" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E158" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F158" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A159" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E159" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F159" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A160" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F160" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A161" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E161" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G161" s="8" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A162" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A163" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E163" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F163" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A164" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E164" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A165" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E165" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F165" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A166" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E166" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F166" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A167" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F167" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A168" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E168" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G168" s="8" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A169" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E169" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G169" s="4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A170" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E170" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F170" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A171" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E171" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G171" s="4" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A172" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E172" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G172" s="4" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A173" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E173" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F173" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A174" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E174" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G174" s="4" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A175" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E175" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F175" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A176" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E176" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F176" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A177" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E177" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F177" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A178" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E178" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F178" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A179" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E179" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F179" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A180" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E180" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F180" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A181" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E181" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G181" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A182" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E182" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F182" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A183" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E183" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F183" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A184" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E184" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F184" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A185" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E185" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G185" s="8" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A186" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E186" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F186" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A187" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E187" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F187" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A188" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B188" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E188" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F188" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A189" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E189" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F189" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A190" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D190" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E190" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F190" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A191" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D191" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E191" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F191" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A192" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D192" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E192" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F192" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A193" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D193" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E193" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F193" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A194" s="6" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C194" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>301</v>
       </c>
@@ -4936,7 +4936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>303</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>306</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
         <v>309</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>310</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>312</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>314</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>315</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>317</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
         <v>319</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>320</v>
       </c>
@@ -5097,7 +5097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>322</v>
       </c>
@@ -5114,7 +5114,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>324</v>
       </c>
@@ -5128,7 +5128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
         <v>325</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>326</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
         <v>327</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>328</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
         <v>330</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
         <v>331</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
         <v>332</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>333</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
         <v>334</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
         <v>335</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>340</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>342</v>
       </c>
@@ -5320,7 +5320,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>344</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>346</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
         <v>349</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
         <v>351</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>353</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>354</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
         <v>356</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>357</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
         <v>359</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>361</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>362</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>364</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="s">
         <v>365</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>367</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
         <v>368</v>
       </c>
@@ -5563,7 +5563,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
         <v>369</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>370</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
         <v>371</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>373</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>374</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
         <v>377</v>
       </c>
@@ -5656,7 +5656,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
         <v>379</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
         <v>381</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="s">
         <v>384</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
         <v>386</v>
       </c>
@@ -5726,11 +5726,14 @@
       <c r="G245" s="11"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G194">
+    <sortCondition ref="A2:A194"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="A134" r:id="rId1" tooltip="Prosthechea aemula" display="http://worldfloraonline.org/taxon/wfo-0000283510" xr:uid="{34AA9517-4D37-48A5-B619-B5E4EB9166F4}"/>
-    <hyperlink ref="G161" r:id="rId2" display="https://stricollections.org/portal/checklists/checklist.php?pagenumber=3&amp;clid=64&amp;dynclid=0&amp;showvouchers=1&amp;pid=20&amp;searchsynonyms=1" xr:uid="{3DD34321-8631-4C7E-B1FB-CDD3F7080BB7}"/>
-    <hyperlink ref="G168" r:id="rId3" display="https://stricollections.org/portal/checklists/checklist.php?pagenumber=3&amp;clid=64&amp;dynclid=0&amp;showvouchers=1&amp;pid=20&amp;searchsynonyms=1" xr:uid="{6D16AED7-CB6E-4C14-B2AB-0646D0607B73}"/>
-    <hyperlink ref="G185" r:id="rId4" display="https://stricollections.org/portal/checklists/checklist.php?pagenumber=3&amp;clid=64&amp;dynclid=0&amp;showvouchers=1&amp;pid=20&amp;searchsynonyms=1" xr:uid="{4DCDEEF4-EDBC-4480-8EF4-58A7F7BFD411}"/>
+    <hyperlink ref="A151" r:id="rId1" tooltip="Prosthechea aemula" display="http://worldfloraonline.org/taxon/wfo-0000283510" xr:uid="{34AA9517-4D37-48A5-B619-B5E4EB9166F4}"/>
+    <hyperlink ref="G132" r:id="rId2" display="https://stricollections.org/portal/checklists/checklist.php?pagenumber=3&amp;clid=64&amp;dynclid=0&amp;showvouchers=1&amp;pid=20&amp;searchsynonyms=1" xr:uid="{3DD34321-8631-4C7E-B1FB-CDD3F7080BB7}"/>
+    <hyperlink ref="G139" r:id="rId3" display="https://stricollections.org/portal/checklists/checklist.php?pagenumber=3&amp;clid=64&amp;dynclid=0&amp;showvouchers=1&amp;pid=20&amp;searchsynonyms=1" xr:uid="{6D16AED7-CB6E-4C14-B2AB-0646D0607B73}"/>
+    <hyperlink ref="G146" r:id="rId4" display="https://stricollections.org/portal/checklists/checklist.php?pagenumber=3&amp;clid=64&amp;dynclid=0&amp;showvouchers=1&amp;pid=20&amp;searchsynonyms=1" xr:uid="{4DCDEEF4-EDBC-4480-8EF4-58A7F7BFD411}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="89" fitToHeight="0" orientation="landscape" r:id="rId5"/>
@@ -5740,22 +5743,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C39B309-997B-4CFD-9DFE-44F8A7F00F12}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="113.1640625" customWidth="1"/>
+    <col min="1" max="1" width="113.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="68" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="160" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>389</v>
       </c>
@@ -5769,47 +5772,47 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CAAFA80-DDFA-4F9E-B18D-472CE9A9C50E}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="112.83203125" style="14" customWidth="1"/>
+    <col min="1" max="1" width="112.85546875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="187" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="51" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>396</v>
       </c>
